--- a/data/seed/portfolio/L-2024-6371/vypiska_2026-07_09.xlsx
+++ b/data/seed/portfolio/L-2024-6371/vypiska_2026-07_09.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J151"/>
+  <dimension ref="A1:J138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -542,456 +542,451 @@
       </c>
       <c r="C8" s="2" t="n"/>
       <c r="D8" s="2" t="n">
-        <v>4597000</v>
+        <v>22211000</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sarbon Yog'och AJ</t>
+          <t>Chust Poligraf MChJ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>205262718</t>
+          <t>326271870</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>20208000045419893001</t>
+          <t>20208000541989361001</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №293/26, QQS 12%</t>
+          <t>Предоплата за товар по договору №182/26 от 01.07.2026</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>37697000</v>
+        <v>55311000</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B9" t="n">
         <v>101</v>
       </c>
-      <c r="C9" s="2" t="n"/>
-      <c r="D9" s="2" t="n">
-        <v>1888000</v>
-      </c>
+      <c r="C9" s="2" t="n">
+        <v>31075000</v>
+      </c>
+      <c r="D9" s="2" t="n"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sarbon Yog'och AJ</t>
+          <t>Nukus Mebel XK</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>205262718</t>
+          <t>327676270</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>20208000045419893001</t>
+          <t>20208000825763345001</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Shartnoma №273/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за сырье по договору №105/26 от 02.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>39585000</v>
+        <v>24236000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>46204</v>
+        <v>46208</v>
       </c>
       <c r="B10" t="n">
         <v>102</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>51264000</v>
+        <v>8400000</v>
       </c>
       <c r="D10" s="2" t="n"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Afrosiyob Plastik MChJ</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>343417049</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-6371)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20208000274057287001</t>
+          <t>16307000301836844417</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Оплата за сырье по дог. №89/26 от 01.07.2026, НДС 12%</t>
+          <t>Kredit shartnomasi L-2024-6371 bo'yicha navbatdagi to'lov (07.2026)</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-11679000</v>
+        <v>15836000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B11" t="n">
         <v>103</v>
       </c>
-      <c r="C11" s="2" t="n">
-        <v>2442000</v>
-      </c>
-      <c r="D11" s="2" t="n"/>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n">
+        <v>4804000</v>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tong Qurilish MChJ</t>
+          <t>Marg'ilon Moy MChJ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>325307809</t>
+          <t>302791508</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20208000468403398001</t>
+          <t>20208000664381878001</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №2350</t>
+          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №5046 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>-14121000</v>
+        <v>20640000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B12" t="n">
         <v>104</v>
       </c>
-      <c r="C12" s="2" t="n">
-        <v>4727000</v>
-      </c>
-      <c r="D12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n">
+        <v>3440000</v>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Shahrisabz Savdo AJ</t>
+          <t>Chust Poligraf MChJ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>341430836</t>
+          <t>326271870</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20208000985060096001</t>
+          <t>20208000541989361001</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №159/26 от 02.07.2026, НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №241/26, QQS 12%</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>-18848000</v>
+        <v>24080000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="B13" t="n">
         <v>105</v>
       </c>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="n">
-        <v>14243000</v>
-      </c>
+      <c r="C13" s="2" t="n">
+        <v>7228000</v>
+      </c>
+      <c r="D13" s="2" t="n"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bunyodkor Avto Savdo AJ</t>
+          <t>Nukus Mebel XK</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>368027915</t>
+          <t>327676270</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20208000856643818001</t>
+          <t>20208000825763345001</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №15/26, QQS 12%</t>
+          <t>Оплата за упаковочные материалы, с/ф №1719</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>-4605000</v>
+        <v>16852000</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="B14" t="n">
         <v>106</v>
       </c>
-      <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2" t="n">
-        <v>3702000</v>
-      </c>
+      <c r="C14" s="2" t="n">
+        <v>10158000</v>
+      </c>
+      <c r="D14" s="2" t="n"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sarbon Yog'och AJ</t>
+          <t>Andijon Yog'och MChJ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>205262718</t>
+          <t>326745874</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20208000045419893001</t>
+          <t>20208000918948325001</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №192/26 от 03.07.2026</t>
+          <t>Оплата за сырье по договору №39/26 от 06.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>-903000</v>
+        <v>6694000</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="B15" t="n">
         <v>107</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>2136000</v>
+        <v>12134000</v>
       </c>
       <c r="D15" s="2" t="n"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Farg'ona Polimer MChJ</t>
+          <t>Oltin Vodiy Non MChJ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>208253873</t>
+          <t>337173119</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20208000580895696001</t>
+          <t>20208000526338527001</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №242/26</t>
+          <t>Оплата за транспортные услуги по дог. №44/26</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>-3039000</v>
+        <v>-5440000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="B16" t="n">
         <v>108</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>2515000</v>
+        <v>17626000</v>
       </c>
       <c r="D16" s="2" t="n"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tong Qurilish MChJ</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>325307809</t>
+          <t>Yangi Asr Bank</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20208000468403398001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №9369</t>
+          <t>Перечисление заработной платы за июнь 2026 г. согласно реестру №2206</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>-5554000</v>
+        <v>-23066000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>46208</v>
+        <v>46210</v>
       </c>
       <c r="B17" t="n">
         <v>109</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>8400000</v>
+        <v>1982000</v>
       </c>
       <c r="D17" s="2" t="n"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-6371)</t>
+          <t>Denov Qurilish MChJ</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>282538733</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>16307000301836844417</t>
+          <t>20208000808956968001</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-6371 bo'yicha navbatdagi to'lov (07.2026)</t>
+          <t>Аренда помещения за июль, дог. №24/25</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>-13954000</v>
+        <v>-25048000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B18" t="n">
         <v>110</v>
       </c>
-      <c r="C18" s="2" t="n"/>
-      <c r="D18" s="2" t="n">
-        <v>30095000</v>
-      </c>
+      <c r="C18" s="2" t="n">
+        <v>59194000</v>
+      </c>
+      <c r="D18" s="2" t="n"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sarbon Yog'och AJ</t>
+          <t>Nukus Mebel XK</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>205262718</t>
+          <t>327676270</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20208000045419893001</t>
+          <t>20208000825763345001</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог №71/26 от 06.07.2026</t>
+          <t>Оплата за упаковочные материалы, с/ф №8291</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>16141000</v>
+        <v>-84242000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>46209</v>
+        <v>46211</v>
       </c>
       <c r="B19" t="n">
         <v>111</v>
       </c>
       <c r="C19" s="2" t="n"/>
       <c r="D19" s="2" t="n">
-        <v>6237000</v>
+        <v>20385000</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sarbon Yog'och AJ</t>
+          <t>Gulshan Sut MChJ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>205262718</t>
+          <t>395063017</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20208000045419893001</t>
+          <t>20208000719687187001</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1001,232 +996,237 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №8203 от 06.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товар по с/ф №1972 от 08.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>22378000</v>
+        <v>-63857000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>46209</v>
+        <v>46212</v>
       </c>
       <c r="B20" t="n">
         <v>112</v>
       </c>
-      <c r="C20" s="2" t="n">
-        <v>17626000</v>
-      </c>
-      <c r="D20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="n">
+        <v>9447000</v>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Yangi Asr Bank</t>
+          <t>Marg'ilon Moy MChJ</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>302791508</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000664381878001</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Ish haqi to'lovi iyun 2026 (plastik kartalarga)</t>
+          <t>Оплата за товар по счет-фактуре №7932 от 09.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>4752000</v>
+        <v>-54410000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>46210</v>
+        <v>46216</v>
       </c>
       <c r="B21" t="n">
         <v>113</v>
       </c>
-      <c r="C21" s="2" t="n">
-        <v>104395000</v>
-      </c>
-      <c r="D21" s="2" t="n"/>
+      <c r="C21" s="2" t="n"/>
+      <c r="D21" s="2" t="n">
+        <v>12106000</v>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Navoiy Yog'och MChJ</t>
+          <t>Chust Poligraf MChJ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>350649569</t>
+          <t>326271870</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20208000649105146001</t>
+          <t>20208000541989361001</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №5/26, QQS bilan</t>
+          <t>Предоплата за товар по дог. №14/26 от 13.07.2026</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>-99643000</v>
+        <v>-42304000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>46211</v>
+        <v>46216</v>
       </c>
       <c r="B22" t="n">
         <v>114</v>
       </c>
       <c r="C22" s="2" t="n"/>
       <c r="D22" s="2" t="n">
-        <v>5023000</v>
+        <v>5381000</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Olmaliq Farm Savdo MChJ</t>
+          <t>Chust Poligraf MChJ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>306131664</t>
+          <t>326271870</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20208000854175652001</t>
+          <t>20208000541989361001</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №69/26, НДС 12%</t>
+          <t>Оплата за продукцию по дог. №285/26, НДС 12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>-94620000</v>
+        <v>-36923000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>46211</v>
+        <v>46217</v>
       </c>
       <c r="B23" t="n">
         <v>115</v>
       </c>
-      <c r="C23" s="2" t="n">
-        <v>1982000</v>
-      </c>
-      <c r="D23" s="2" t="n"/>
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="2" t="n">
+        <v>4914000</v>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Marg'ilon Qurilish MChJ</t>
+          <t>Marg'ilon Moy MChJ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>354150901</t>
+          <t>302791508</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20208000960261721001</t>
+          <t>20208000664381878001</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>АРЕНДНАЯ ПЛАТА ЗА ИЮЛЬ 2026 Г. ПО ДОГОВОРУ №77/23</t>
+          <t>Оплата по счет-фктуре №4294 за поставленный товар</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>-96602000</v>
+        <v>-32009000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>46213</v>
+        <v>46217</v>
       </c>
       <c r="B24" t="n">
         <v>116</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>2179000</v>
+        <v>14850000</v>
       </c>
       <c r="D24" s="2" t="n"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Afrosiyob Plastik MChJ</t>
+          <t>Nukus Mebel XK</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>343417049</t>
+          <t>327676270</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20208000274057287001</t>
+          <t>20208000825763345001</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно с/ф №3980</t>
+          <t>Предоплата за материалы по договору №105/26</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>-98781000</v>
+        <v>-46859000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>46213</v>
+        <v>46218</v>
       </c>
       <c r="B25" t="n">
         <v>117</v>
       </c>
-      <c r="C25" s="2" t="n">
-        <v>2447000</v>
-      </c>
-      <c r="D25" s="2" t="n"/>
+      <c r="C25" s="2" t="n"/>
+      <c r="D25" s="2" t="n">
+        <v>3908000</v>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Farg'ona Polimer MChJ</t>
+          <t>Chust Poligraf MChJ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>208253873</t>
+          <t>326271870</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20208000580895696001</t>
+          <t>20208000541989361001</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1236,157 +1236,157 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №202/26</t>
+          <t>Оплата по счет-фактуре №2032 за поставленный товар</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>-101228000</v>
+        <v>-42951000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="B26" t="n">
         <v>118</v>
       </c>
-      <c r="C26" s="2" t="n"/>
-      <c r="D26" s="2" t="n">
-        <v>13169000</v>
-      </c>
+      <c r="C26" s="2" t="n">
+        <v>2403000</v>
+      </c>
+      <c r="D26" s="2" t="n"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sarbon Yog'och AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>205262718</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20208000045419893001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №3235 от 13.07.2026, в т.ч. НДС 12%</t>
+          <t>Уплата социального налога за июнь</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>-88059000</v>
+        <v>-45354000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="B27" t="n">
         <v>119</v>
       </c>
-      <c r="C27" s="2" t="n"/>
-      <c r="D27" s="2" t="n">
-        <v>3469000</v>
-      </c>
+      <c r="C27" s="2" t="n">
+        <v>2403000</v>
+      </c>
+      <c r="D27" s="2" t="n"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Namangan Plastik MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>218371731</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20208000915263385001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Оплата з товар по счет-фактуре №8983 от 13.07.2026, в т.ч. НДС 12%</t>
+          <t>Налог на доходы физических иц за июнь 2026 г.</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>-84590000</v>
+        <v>-47757000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>46216</v>
+        <v>46219</v>
       </c>
       <c r="B28" t="n">
         <v>120</v>
       </c>
       <c r="C28" s="2" t="n"/>
       <c r="D28" s="2" t="n">
-        <v>1785000</v>
+        <v>6206000</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bunyodkor Avto Savdo AJ</t>
+          <t>Chust Poligraf MChJ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>368027915</t>
+          <t>326271870</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20208000856643818001</t>
+          <t>20208000541989361001</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №173/26 от 13.07.2026</t>
+          <t>Оплата за товар по счет-фактуре №3472 от 16.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>-82805000</v>
+        <v>-41551000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>46216</v>
+        <v>46220</v>
       </c>
       <c r="B29" t="n">
         <v>121</v>
       </c>
-      <c r="C29" s="2" t="n">
-        <v>5885000</v>
-      </c>
-      <c r="D29" s="2" t="n"/>
+      <c r="C29" s="2" t="n"/>
+      <c r="D29" s="2" t="n">
+        <v>6082000</v>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Farg'ona Polimer MChJ</t>
+          <t>Chust Poligraf MChJ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>208253873</t>
+          <t>326271870</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20208000580895696001</t>
+          <t>20208000541989361001</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1396,957 +1396,947 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно с/ф №5545</t>
+          <t>Shartnoma №207/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>-88690000</v>
+        <v>-35469000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>46217</v>
+        <v>46220</v>
       </c>
       <c r="B30" t="n">
         <v>122</v>
       </c>
       <c r="C30" s="2" t="n"/>
       <c r="D30" s="2" t="n">
-        <v>13215000</v>
+        <v>4224000</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sarbon Yog'och AJ</t>
+          <t>Chust Poligraf MChJ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>205262718</t>
+          <t>326271870</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20208000045419893001</t>
+          <t>20208000541989361001</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №1741 за поставленный товар</t>
+          <t>Предоплата за товар по договору №93/26 от 17.07.2026</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>-75475000</v>
+        <v>-31245000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>46217</v>
+        <v>46223</v>
       </c>
       <c r="B31" t="n">
         <v>123</v>
       </c>
       <c r="C31" s="2" t="n"/>
       <c r="D31" s="2" t="n">
-        <v>9630000</v>
+        <v>42628000</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Navoiy Non AJ</t>
+          <t>Gulshan Sut MChJ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>313296393</t>
+          <t>395063017</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20208000809153157001</t>
+          <t>20208000719687187001</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №2513 за поставленный товар</t>
+          <t>Оплата за товар по счет-фактуре №5496 от 20.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>-65845000</v>
+        <v>11383000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>46217</v>
+        <v>46223</v>
       </c>
       <c r="B32" t="n">
         <v>124</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>2403000</v>
+        <v>19264000</v>
       </c>
       <c r="D32" s="2" t="n"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Oltin Vodiy Non MChJ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>337173119</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000526338527001</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Социальный налог за июнь 2026 г.</t>
+          <t>ОПЛАТА ЗА СЫРЬЕ ПО ДОГОВОРУ №279/26 ОТ 20.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>-68248000</v>
+        <v>-7881000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>46217</v>
+        <v>46223</v>
       </c>
       <c r="B33" t="n">
         <v>125</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>2403000</v>
+        <v>22620000</v>
       </c>
       <c r="D33" s="2" t="n"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Saodat Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>241704982</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000405728734001</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Налог на доходы физических лиц за июнь 2026 г.</t>
+          <t>Оплата за сырье по договору №197/26 от 20.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>-70651000</v>
+        <v>-30501000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>46218</v>
+        <v>46224</v>
       </c>
       <c r="B34" t="n">
         <v>126</v>
       </c>
-      <c r="C34" s="2" t="n"/>
-      <c r="D34" s="2" t="n">
-        <v>10511000</v>
-      </c>
+      <c r="C34" s="2" t="n">
+        <v>3282000</v>
+      </c>
+      <c r="D34" s="2" t="n"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bunyodkor Avto Savdo AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>368027915</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>20208000856643818001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №1360 от 15.07.2026, в т.ч. НДС 12%</t>
+          <t>Уплата налога на добавленную стоимость за июнь</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>-60140000</v>
+        <v>-33783000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>46220</v>
+        <v>46226</v>
       </c>
       <c r="B35" t="n">
         <v>127</v>
       </c>
-      <c r="C35" s="2" t="n">
-        <v>7199000</v>
-      </c>
-      <c r="D35" s="2" t="n"/>
+      <c r="C35" s="2" t="n"/>
+      <c r="D35" s="2" t="n">
+        <v>72794000</v>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Farg'ona Polimer MChJ</t>
+          <t>Marg'ilon Moy MChJ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>208253873</t>
+          <t>302791508</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>20208000580895696001</t>
+          <t>20208000664381878001</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по дог. №231/26</t>
+          <t>Оплата за продукцию по договору №127/26, НДС 12%</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>-67339000</v>
+        <v>39011000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>46223</v>
+        <v>46227</v>
       </c>
       <c r="B36" t="n">
         <v>128</v>
       </c>
-      <c r="C36" s="2" t="n"/>
-      <c r="D36" s="2" t="n">
-        <v>51398000</v>
-      </c>
+      <c r="C36" s="2" t="n">
+        <v>18582000</v>
+      </c>
+      <c r="D36" s="2" t="n"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sarbon Yog'och AJ</t>
+          <t>Oltin Vodiy Non MChJ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>205262718</t>
+          <t>337173119</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20208000045419893001</t>
+          <t>20208000526338527001</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>SHARTNOMA №136/26 BO'YICHA OLDINDAN TO'LOV</t>
+          <t>Оплата за сырье по договору №57/26 от 24.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>-15941000</v>
+        <v>20429000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>46223</v>
+        <v>46227</v>
       </c>
       <c r="B37" t="n">
         <v>129</v>
       </c>
-      <c r="C37" s="2" t="n"/>
-      <c r="D37" s="2" t="n">
-        <v>3385000</v>
-      </c>
+      <c r="C37" s="2" t="n">
+        <v>36876000</v>
+      </c>
+      <c r="D37" s="2" t="n"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sarbon Yog'och AJ</t>
+          <t>Oltin Vodiy Non MChJ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>205262718</t>
+          <t>337173119</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20208000045419893001</t>
+          <t>20208000526338527001</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №224/26, НДС 12%</t>
+          <t>Оплата за сырье по договору №272/26 от 24.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>-12556000</v>
+        <v>-16447000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="B38" t="n">
         <v>130</v>
       </c>
-      <c r="C38" s="2" t="n">
-        <v>2495000</v>
-      </c>
-      <c r="D38" s="2" t="n"/>
+      <c r="C38" s="2" t="n"/>
+      <c r="D38" s="2" t="n">
+        <v>13767000</v>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Afrosiyob Plastik MChJ</t>
+          <t>Omad Yog'och MChJ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>343417049</t>
+          <t>336272115</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>20208000274057287001</t>
+          <t>20208000872013636001</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №9921</t>
+          <t>Оплата по счет-фактуре №6729 за поставленный товар</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>-15051000</v>
+        <v>-2680000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>46224</v>
+        <v>46230</v>
       </c>
       <c r="B39" t="n">
         <v>131</v>
       </c>
       <c r="C39" s="2" t="n"/>
       <c r="D39" s="2" t="n">
-        <v>4884000</v>
+        <v>3591000</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bunyodkor Avto Savdo AJ</t>
+          <t>Chust Poligraf MChJ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>368027915</t>
+          <t>326271870</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20208000856643818001</t>
+          <t>20208000541989361001</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №228/26 от 21.07.2026</t>
+          <t>Tovar uchun to'lov, hisob-faktura №2700 27.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>-10167000</v>
+        <v>911000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>46224</v>
+        <v>46230</v>
       </c>
       <c r="B40" t="n">
         <v>132</v>
       </c>
       <c r="C40" s="2" t="n">
-        <v>8888000</v>
+        <v>1239000</v>
       </c>
       <c r="D40" s="2" t="n"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Navoiy Yog'och MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>350649569</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20208000649105146001</t>
+          <t>20208000685415090001</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №163/26</t>
+          <t>Elektr energiyasi uchun to'lov</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>-19055000</v>
+        <v>-328000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>46225</v>
+        <v>46231</v>
       </c>
       <c r="B41" t="n">
         <v>133</v>
       </c>
       <c r="C41" s="2" t="n"/>
       <c r="D41" s="2" t="n">
-        <v>16548000</v>
+        <v>13641000</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Sarbon Yog'och AJ</t>
+          <t>Marg'ilon Moy MChJ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>205262718</t>
+          <t>302791508</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20208000045419893001</t>
+          <t>20208000664381878001</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №74/26 от 22.07.2026</t>
+          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №243/26, QQS 12%</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>-2507000</v>
+        <v>13313000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>46225</v>
+        <v>46233</v>
       </c>
       <c r="B42" t="n">
         <v>134</v>
       </c>
       <c r="C42" s="2" t="n"/>
       <c r="D42" s="2" t="n">
-        <v>3391000</v>
+        <v>16892000</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Olmaliq Farm Savdo MChJ</t>
+          <t>Chust Poligraf MChJ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>306131664</t>
+          <t>326271870</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20208000854175652001</t>
+          <t>20208000541989361001</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №9394 от 22.07.2026, в т.ч. НДС 12%</t>
+          <t>Предоплата за товар по договору №173/26 от 30.07.2026</t>
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>884000</v>
+        <v>30205000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>46225</v>
+        <v>46233</v>
       </c>
       <c r="B43" t="n">
         <v>135</v>
       </c>
-      <c r="C43" s="2" t="n">
-        <v>3348000</v>
-      </c>
-      <c r="D43" s="2" t="n"/>
+      <c r="C43" s="2" t="n"/>
+      <c r="D43" s="2" t="n">
+        <v>3773000</v>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Chust Poligraf MChJ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>326271870</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000541989361001</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>НДС за июнь 2026 г.</t>
+          <t>Предоплата за товар по договору №104/26 от 30.07.2026</t>
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>-2464000</v>
+        <v>33978000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>46225</v>
+        <v>46233</v>
       </c>
       <c r="B44" t="n">
         <v>136</v>
       </c>
-      <c r="C44" s="2" t="n">
-        <v>11683000</v>
-      </c>
-      <c r="D44" s="2" t="n"/>
+      <c r="C44" s="2" t="n"/>
+      <c r="D44" s="2" t="n">
+        <v>3297000</v>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Tong Qurilish MChJ</t>
+          <t>Marg'ilon Moy MChJ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>325307809</t>
+          <t>302791508</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20208000468403398001</t>
+          <t>20208000664381878001</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТРАНСПОРТНЫЕ УСЛУГИ ПО ДОГ. №60/26</t>
+          <t>Оплата за товар по счет-фактуре №8957 от 30.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>-14147000</v>
+        <v>37275000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>46226</v>
+        <v>46233</v>
       </c>
       <c r="B45" t="n">
         <v>137</v>
       </c>
-      <c r="C45" s="2" t="n"/>
-      <c r="D45" s="2" t="n">
-        <v>6291000</v>
-      </c>
+      <c r="C45" s="2" t="n">
+        <v>12617000</v>
+      </c>
+      <c r="D45" s="2" t="n"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Olmaliq Farm Savdo MChJ</t>
+          <t>Oltin Vodiy Non MChJ</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>306131664</t>
+          <t>337173119</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20208000854175652001</t>
+          <t>20208000526338527001</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №5893 от 23.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за упаковочные материалы, с/ф №3283</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>-7856000</v>
+        <v>24658000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>46226</v>
+        <v>46234</v>
       </c>
       <c r="B46" t="n">
         <v>138</v>
       </c>
-      <c r="C46" s="2" t="n"/>
-      <c r="D46" s="2" t="n">
-        <v>4294000</v>
-      </c>
+      <c r="C46" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D46" s="2" t="n"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Olmaliq Farm Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>306131664</t>
+          <t>Yangi Asr Bank</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20208000854175652001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №4703 за поставленный товар</t>
+          <t>Комиссия за перевод</t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>-3562000</v>
+        <v>24358000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>46226</v>
+        <v>46237</v>
       </c>
       <c r="B47" t="n">
         <v>139</v>
       </c>
-      <c r="C47" s="2" t="n">
-        <v>4103000</v>
-      </c>
-      <c r="D47" s="2" t="n"/>
+      <c r="C47" s="2" t="n"/>
+      <c r="D47" s="2" t="n">
+        <v>2172000</v>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Farg'ona Polimer MChJ</t>
+          <t>Marg'ilon Moy MChJ</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>208253873</t>
+          <t>302791508</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20208000580895696001</t>
+          <t>20208000664381878001</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №289/26</t>
+          <t>Оплата за товар по счет-фактуре №5094 от 03.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>-7665000</v>
+        <v>26530000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>46227</v>
+        <v>46237</v>
       </c>
       <c r="B48" t="n">
         <v>140</v>
       </c>
-      <c r="C48" s="2" t="n">
-        <v>1239000</v>
-      </c>
-      <c r="D48" s="2" t="n"/>
+      <c r="C48" s="2" t="n"/>
+      <c r="D48" s="2" t="n">
+        <v>1126000</v>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Chust Poligraf MChJ</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>326271870</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20208000898561412001</t>
+          <t>20208000541989361001</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Оплата за электроэнергию согласно счету</t>
+          <t>Оплата за товар по счет-фактуре №759 от 03.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>-8904000</v>
+        <v>27656000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="B49" t="n">
         <v>141</v>
       </c>
-      <c r="C49" s="2" t="n"/>
-      <c r="D49" s="2" t="n">
-        <v>8565000</v>
-      </c>
+      <c r="C49" s="2" t="n">
+        <v>16895000</v>
+      </c>
+      <c r="D49" s="2" t="n"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sarbon Yog'och AJ</t>
+          <t>Andijon Yog'och MChJ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>205262718</t>
+          <t>326745874</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20208000045419893001</t>
+          <t>20208000918948325001</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №2371 от 27.07.2026, в т.ч. НДС 12%</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №35/26, QQS bilan</t>
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>-339000</v>
+        <v>10761000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
-        <v>46230</v>
+        <v>46238</v>
       </c>
       <c r="B50" t="n">
         <v>142</v>
       </c>
-      <c r="C50" s="2" t="n"/>
-      <c r="D50" s="2" t="n">
-        <v>6294000</v>
-      </c>
+      <c r="C50" s="2" t="n">
+        <v>5564000</v>
+      </c>
+      <c r="D50" s="2" t="n"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sarbon Yog'och AJ</t>
+          <t>Oltin Vodiy Non MChJ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>205262718</t>
+          <t>337173119</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20208000045419893001</t>
+          <t>20208000526338527001</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №9674</t>
+          <t>Предоплата за материалы по дог. №9/26</t>
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>5955000</v>
+        <v>5197000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
-        <v>46230</v>
+        <v>46239</v>
       </c>
       <c r="B51" t="n">
         <v>143</v>
       </c>
       <c r="C51" s="2" t="n"/>
       <c r="D51" s="2" t="n">
-        <v>5169000</v>
+        <v>3875000</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sarbon Yog'och AJ</t>
+          <t>Chust Poligraf MChJ</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>205262718</t>
+          <t>326271870</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20208000045419893001</t>
+          <t>20208000541989361001</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №3795 за поставленный товар</t>
+          <t>Оплата за товар по счет-фактуре №5411 от 05.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>11124000</v>
+        <v>9072000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
-        <v>46230</v>
+        <v>46239</v>
       </c>
       <c r="B52" t="n">
         <v>144</v>
       </c>
-      <c r="C52" s="2" t="n">
-        <v>6080000</v>
-      </c>
-      <c r="D52" s="2" t="n"/>
+      <c r="C52" s="2" t="n"/>
+      <c r="D52" s="2" t="n">
+        <v>618000</v>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Farg'ona Polimer MChJ</t>
+          <t>Farg'ona Yog'och MChJ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>208253873</t>
+          <t>313166428</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>20208000580895696001</t>
+          <t>20208000417565217001</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №287/26</t>
+          <t>Предоплата за товар по договору №180/26 от 05.08.2026</t>
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>5044000</v>
+        <v>9690000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
-        <v>46232</v>
+        <v>46239</v>
       </c>
       <c r="B53" t="n">
         <v>145</v>
       </c>
-      <c r="C53" s="2" t="n"/>
-      <c r="D53" s="2" t="n">
-        <v>29342000</v>
-      </c>
+      <c r="C53" s="2" t="n">
+        <v>8400000</v>
+      </c>
+      <c r="D53" s="2" t="n"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sarbon Yog'och AJ</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>205262718</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-6371)</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>20208000045419893001</t>
+          <t>16307000301836844417</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2356,547 +2346,552 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №6107 за поставленный товар</t>
+          <t>Kredit shartnomasi L-2024-6371 bo'yicha navbatdagi to'lov (08.2026)</t>
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>34386000</v>
+        <v>1290000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
-        <v>46232</v>
+        <v>46239</v>
       </c>
       <c r="B54" t="n">
         <v>146</v>
       </c>
-      <c r="C54" s="2" t="n"/>
-      <c r="D54" s="2" t="n">
-        <v>5718000</v>
-      </c>
+      <c r="C54" s="2" t="n">
+        <v>17221000</v>
+      </c>
+      <c r="D54" s="2" t="n"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Bunyodkor Avto Savdo AJ</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>368027915</t>
+          <t>Yangi Asr Bank</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>20208000856643818001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovaruchun to'lov h/f №6457</t>
+          <t>Ish haqi to'lovi iyul 2026 (plastik kartalarga)</t>
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>40104000</v>
+        <v>-15931000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
-        <v>46232</v>
+        <v>46240</v>
       </c>
       <c r="B55" t="n">
         <v>147</v>
       </c>
       <c r="C55" s="2" t="n"/>
       <c r="D55" s="2" t="n">
-        <v>3799000</v>
+        <v>1741000</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Toshkent Farm Savdo MChJ</t>
+          <t>Marg'ilon Moy MChJ</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>208950630</t>
+          <t>302791508</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>20208000777196871001</t>
+          <t>20208000664381878001</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №223/26, НДС 12%</t>
+          <t>Предоплата за товар по договору №267/26 от 06.08.2026</t>
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>43903000</v>
+        <v>-14190000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
-        <v>46232</v>
+        <v>46240</v>
       </c>
       <c r="B56" t="n">
         <v>148</v>
       </c>
       <c r="C56" s="2" t="n"/>
       <c r="D56" s="2" t="n">
-        <v>2664000</v>
+        <v>1554000</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Bunyodkor Avto Savdo AJ</t>
+          <t>Farg'ona Yog'och MChJ</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>368027915</t>
+          <t>313166428</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>20208000856643818001</t>
+          <t>20208000417565217001</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №6764 от 29.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товар по с/ф №8866 от 06.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>46567000</v>
+        <v>-12636000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
-        <v>46232</v>
+        <v>46240</v>
       </c>
       <c r="B57" t="n">
         <v>149</v>
       </c>
-      <c r="C57" s="2" t="n">
-        <v>8339000</v>
-      </c>
-      <c r="D57" s="2" t="n"/>
+      <c r="C57" s="2" t="n"/>
+      <c r="D57" s="2" t="n">
+        <v>924000</v>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Farg'ona Polimer MChJ</t>
+          <t>Farg'ona Yog'och MChJ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>208253873</t>
+          <t>313166428</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>20208000580895696001</t>
+          <t>20208000417565217001</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №8950</t>
+          <t>Предоплата за товар по договору №149/26 от 06.08.2026</t>
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>38228000</v>
+        <v>-11712000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
-        <v>46233</v>
+        <v>46240</v>
       </c>
       <c r="B58" t="n">
         <v>150</v>
       </c>
-      <c r="C58" s="2" t="n"/>
-      <c r="D58" s="2" t="n">
-        <v>9719000</v>
-      </c>
+      <c r="C58" s="2" t="n">
+        <v>19559000</v>
+      </c>
+      <c r="D58" s="2" t="n"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Sarbon Yog'och AJ</t>
+          <t>Oltin Vodiy Non MChJ</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>205262718</t>
+          <t>337173119</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>20208000045419893001</t>
+          <t>20208000526338527001</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №7644 за поставленный товар</t>
+          <t>Оплата за транспортные услуги по договору №205/26</t>
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>47947000</v>
+        <v>-31271000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
-        <v>46233</v>
+        <v>46244</v>
       </c>
       <c r="B59" t="n">
         <v>151</v>
       </c>
-      <c r="C59" s="2" t="n">
-        <v>3015000</v>
-      </c>
-      <c r="D59" s="2" t="n"/>
+      <c r="C59" s="2" t="n"/>
+      <c r="D59" s="2" t="n">
+        <v>3527000</v>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Shahrisabz Savdo AJ</t>
+          <t>Chust Poligraf MChJ</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>341430836</t>
+          <t>326271870</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>20208000985060096001</t>
+          <t>20208000541989361001</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно с/ф №4638</t>
+          <t>Tovar uchun to'lov, hisob-faktura №9433 10.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>44932000</v>
+        <v>-27744000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
-        <v>46234</v>
+        <v>46244</v>
       </c>
       <c r="B60" t="n">
         <v>152</v>
       </c>
-      <c r="C60" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D60" s="2" t="n"/>
+      <c r="C60" s="2" t="n"/>
+      <c r="D60" s="2" t="n">
+        <v>2934000</v>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Yangi Asr Bank</t>
+          <t>Chust Poligraf MChJ</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>326271870</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000541989361001</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Плата за SMS-информирование</t>
+          <t>Оплата по счет-фактуре №5034 за поставленный товар</t>
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>44632000</v>
+        <v>-24810000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
-        <v>46234</v>
+        <v>46244</v>
       </c>
       <c r="B61" t="n">
         <v>153</v>
       </c>
       <c r="C61" s="2" t="n">
-        <v>12661000</v>
+        <v>1937000</v>
       </c>
       <c r="D61" s="2" t="n"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Tong Qurilish MChJ</t>
+          <t>Denov Qurilish MChJ</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>325307809</t>
+          <t>282538733</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>20208000468403398001</t>
+          <t>20208000808956968001</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №9490</t>
+          <t>Аренда помещения за август, дог. №24/25</t>
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>31971000</v>
+        <v>-26747000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="B62" t="n">
         <v>154</v>
       </c>
-      <c r="C62" s="2" t="n"/>
-      <c r="D62" s="2" t="n">
-        <v>48123000</v>
-      </c>
+      <c r="C62" s="2" t="n">
+        <v>5136000</v>
+      </c>
+      <c r="D62" s="2" t="n"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Sarbon Yog'och AJ</t>
+          <t>Andijon Yog'och MChJ</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>205262718</t>
+          <t>326745874</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>20208000045419893001</t>
+          <t>20208000918948325001</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №74/26, НДС 12%</t>
+          <t>Materiallar uchun oldindan to'lov, shartn. №155/26</t>
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>80094000</v>
+        <v>-31883000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="B63" t="n">
         <v>155</v>
       </c>
-      <c r="C63" s="2" t="n"/>
-      <c r="D63" s="2" t="n">
-        <v>26242000</v>
-      </c>
+      <c r="C63" s="2" t="n">
+        <v>8230000</v>
+      </c>
+      <c r="D63" s="2" t="n"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Sarbon Yog'och AJ</t>
+          <t>Oltin Vodiy Non MChJ</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>205262718</t>
+          <t>337173119</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>20208000045419893001</t>
+          <t>20208000526338527001</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №198/26, НДС 12%</t>
+          <t>Оплата за товары согласно счет-фактуре №580</t>
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>106336000</v>
+        <v>-40113000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="B64" t="n">
         <v>156</v>
       </c>
-      <c r="C64" s="2" t="n"/>
-      <c r="D64" s="2" t="n">
-        <v>12916000</v>
-      </c>
+      <c r="C64" s="2" t="n">
+        <v>25251000</v>
+      </c>
+      <c r="D64" s="2" t="n"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Sarbon Yog'och AJ</t>
+          <t>Oltin Vodiy Non MChJ</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>205262718</t>
+          <t>337173119</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>20208000045419893001</t>
+          <t>20208000526338527001</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №248/26, НДС 12%</t>
+          <t>Оплата за транспортные услуги по договору №269/26</t>
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>119252000</v>
+        <v>-65364000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
-        <v>46237</v>
+        <v>46245</v>
       </c>
       <c r="B65" t="n">
         <v>157</v>
       </c>
       <c r="C65" s="2" t="n">
-        <v>38102000</v>
+        <v>15408000</v>
       </c>
       <c r="D65" s="2" t="n"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Tong Qurilish MChJ</t>
+          <t>Nukus Mebel XK</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>325307809</t>
+          <t>327676270</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>20208000468403398001</t>
+          <t>20208000825763345001</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №35/26, QQS bilan</t>
+          <t>Оплата за сырье по договору №129/26 от 11.08.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>81150000</v>
+        <v>-80772000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
-        <v>46238</v>
+        <v>46247</v>
       </c>
       <c r="B66" t="n">
         <v>158</v>
       </c>
-      <c r="C66" s="2" t="n">
-        <v>9669000</v>
-      </c>
-      <c r="D66" s="2" t="n"/>
+      <c r="C66" s="2" t="n"/>
+      <c r="D66" s="2" t="n">
+        <v>23240000</v>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Afrosiyob Plastik MChJ</t>
+          <t>Omad Yog'och MChJ</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>343417049</t>
+          <t>336272115</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>20208000274057287001</t>
+          <t>20208000872013636001</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по дог. №9/26</t>
+          <t>Предоплата за товар по договору №143/26 от 13.08.2026</t>
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>71481000</v>
+        <v>-57532000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
-        <v>46238</v>
+        <v>46248</v>
       </c>
       <c r="B67" t="n">
         <v>159</v>
       </c>
       <c r="C67" s="2" t="n">
-        <v>17221000</v>
+        <v>7521000</v>
       </c>
       <c r="D67" s="2" t="n"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Yangi Asr Bank</t>
+          <t>Saodat Un Mahsulotlari MChJ</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>241704982</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000405728734001</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -2906,112 +2901,117 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Перечисление заработной платы за июль 2026 г. согласно реестру №3311</t>
+          <t>Оплата за сырье по договору №159/26 от 14.08.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>54260000</v>
+        <v>-65053000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
-        <v>46239</v>
+        <v>46251</v>
       </c>
       <c r="B68" t="n">
         <v>160</v>
       </c>
-      <c r="C68" s="2" t="n">
-        <v>8400000</v>
-      </c>
-      <c r="D68" s="2" t="n"/>
+      <c r="C68" s="2" t="n"/>
+      <c r="D68" s="2" t="n">
+        <v>167436000</v>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-6371)</t>
+          <t>Chust Poligraf MChJ</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>326271870</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>16307000301836844417</t>
+          <t>20208000541989361001</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-6371 bo'yicha navbatdagi to'lov (08.2026)</t>
+          <t>Mahsulot uchun to'lov, shartnoma №97/26, QQS 12%</t>
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>45860000</v>
+        <v>102383000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
-        <v>46240</v>
+        <v>46251</v>
       </c>
       <c r="B69" t="n">
         <v>161</v>
       </c>
       <c r="C69" s="2" t="n"/>
       <c r="D69" s="2" t="n">
-        <v>10212000</v>
+        <v>11212000</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Sarbon Yog'och AJ</t>
+          <t>Marg'ilon Moy MChJ</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>205262718</t>
+          <t>302791508</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>20208000045419893001</t>
+          <t>20208000664381878001</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №8181 от 06.08.2026, в т.ч. НДС 12%</t>
+          <t>Предоплата за товар по дог. №193/26 от 17.08.2026</t>
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>56072000</v>
+        <v>113595000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="n">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="B70" t="n">
         <v>162</v>
       </c>
       <c r="C70" s="2" t="n"/>
       <c r="D70" s="2" t="n">
-        <v>2963000</v>
+        <v>1984000</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Sarbon Yog'och AJ</t>
+          <t>Omad Yog'och MChJ</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>205262718</t>
+          <t>336272115</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>20208000045419893001</t>
+          <t>20208000872013636001</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3021,437 +3021,437 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №229/26 от 10.08.2026</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №7513</t>
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>59035000</v>
+        <v>115579000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="B71" t="n">
         <v>163</v>
       </c>
       <c r="C71" s="2" t="n">
-        <v>1937000</v>
+        <v>2348000</v>
       </c>
       <c r="D71" s="2" t="n"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Marg'ilon Qurilish MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>354150901</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>20208000960261721001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Bino ijarasi uchun to'lov avgust</t>
+          <t>Уплата социального налога за июль</t>
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>57098000</v>
+        <v>113231000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="n">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="B72" t="n">
         <v>164</v>
       </c>
       <c r="C72" s="2" t="n">
-        <v>55385000</v>
+        <v>2348000</v>
       </c>
       <c r="D72" s="2" t="n"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Shahrisabz Savdo AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>341430836</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>20208000985060096001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №6727</t>
+          <t>НАЛОГ НА ДОХОДЫ ФИЗИЧЕСКИХ ЛИЦ ЗА ИЮЛЬ 2026 Г.</t>
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>1713000</v>
+        <v>110883000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="n">
-        <v>46245</v>
+        <v>46251</v>
       </c>
       <c r="B73" t="n">
         <v>165</v>
       </c>
       <c r="C73" s="2" t="n">
-        <v>10860000</v>
+        <v>29144000</v>
       </c>
       <c r="D73" s="2" t="n"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Afrosiyob Plastik MChJ</t>
+          <t>Oltin Vodiy Non MChJ</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>343417049</t>
+          <t>337173119</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>20208000274057287001</t>
+          <t>20208000526338527001</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Оплата за транспорные услуги по договору №96/26</t>
+          <t>Оплата за транспортные услуги по дог. №109/26</t>
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>-9147000</v>
+        <v>81739000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="n">
-        <v>46247</v>
+        <v>46253</v>
       </c>
       <c r="B74" t="n">
         <v>166</v>
       </c>
       <c r="C74" s="2" t="n"/>
       <c r="D74" s="2" t="n">
-        <v>2977000</v>
+        <v>14246000</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Sarbon Yog'och AJ</t>
+          <t>Marg'ilon Moy MChJ</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>205262718</t>
+          <t>302791508</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>20208000045419893001</t>
+          <t>20208000664381878001</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №493 за поставленный товар</t>
+          <t>Предоплата за товар по договору №19/26 от 19.08.2026</t>
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>-6170000</v>
+        <v>95985000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="n">
-        <v>46248</v>
+        <v>46253</v>
       </c>
       <c r="B75" t="n">
         <v>167</v>
       </c>
       <c r="C75" s="2" t="n">
-        <v>22493000</v>
+        <v>9622000</v>
       </c>
       <c r="D75" s="2" t="n"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Afrosiyob Plastik MChJ</t>
+          <t>Oltin Vodiy Non MChJ</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>343417049</t>
+          <t>337173119</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>20208000274057287001</t>
+          <t>20208000526338527001</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №159/26 от 14.08.2026, НДС 12%</t>
+          <t>Оплата за транспортные услуги по договору №297/26</t>
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>-28663000</v>
+        <v>86363000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="n">
-        <v>46251</v>
+        <v>46254</v>
       </c>
       <c r="B76" t="n">
         <v>168</v>
       </c>
       <c r="C76" s="2" t="n">
-        <v>2348000</v>
+        <v>5632000</v>
       </c>
       <c r="D76" s="2" t="n"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Oltin Vodiy Non MChJ</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>337173119</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000526338527001</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Уплата социального налога за июль</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №64/26</t>
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>-31011000</v>
+        <v>80731000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="n">
-        <v>46251</v>
+        <v>46254</v>
       </c>
       <c r="B77" t="n">
         <v>169</v>
       </c>
       <c r="C77" s="2" t="n">
-        <v>2348000</v>
+        <v>13028000</v>
       </c>
       <c r="D77" s="2" t="n"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Andijon Yog'och MChJ</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>326745874</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000918948325001</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Налог на доходы физических лиц за июль 2026 г.</t>
+          <t>Оплата за товары согласно счет-фактуре №6179</t>
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>-33359000</v>
+        <v>67703000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="n">
-        <v>46252</v>
+        <v>46255</v>
       </c>
       <c r="B78" t="n">
         <v>170</v>
       </c>
-      <c r="C78" s="2" t="n">
-        <v>29558000</v>
-      </c>
-      <c r="D78" s="2" t="n"/>
+      <c r="C78" s="2" t="n"/>
+      <c r="D78" s="2" t="n">
+        <v>681000</v>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Tong Qurilish MChJ</t>
+          <t>Chust Poligraf MChJ</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>325307809</t>
+          <t>326271870</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>20208000468403398001</t>
+          <t>20208000541989361001</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №37/26 от 18.08.2026, НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartn. №245/26, QQS 12%</t>
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>-62917000</v>
+        <v>68384000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="B79" t="n">
         <v>171</v>
       </c>
-      <c r="C79" s="2" t="n"/>
-      <c r="D79" s="2" t="n">
-        <v>12608000</v>
-      </c>
+      <c r="C79" s="2" t="n">
+        <v>14543000</v>
+      </c>
+      <c r="D79" s="2" t="n"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Toshkent Savdo XK</t>
+          <t>Durdona Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>266276762</t>
+          <t>264956936</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>20208000028257633001</t>
+          <t>20208000910514646001</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №3649 за поставленный товар</t>
+          <t>ОПЛАТА ЗА СЫРЬЕ ПО ДОГОВОРУ №286/26 ОТ 21.08.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>-50309000</v>
+        <v>53841000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="n">
-        <v>46254</v>
+        <v>46258</v>
       </c>
       <c r="B80" t="n">
         <v>172</v>
       </c>
-      <c r="C80" s="2" t="n"/>
-      <c r="D80" s="2" t="n">
-        <v>34236000</v>
-      </c>
+      <c r="C80" s="2" t="n">
+        <v>3127000</v>
+      </c>
+      <c r="D80" s="2" t="n"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Sarbon Yog'och AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>205262718</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>20208000045419893001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №7772 от 20.08.2026, в т.ч. НДС 12%</t>
+          <t>УПЛАТА НАЛОГА НА ДОБАВЛЕННУЮ СТОИМОСТЬ ЗА ИЮЛЬ</t>
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>-16073000</v>
+        <v>50714000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="n">
-        <v>46254</v>
+        <v>46258</v>
       </c>
       <c r="B81" t="n">
         <v>173</v>
       </c>
-      <c r="C81" s="2" t="n"/>
-      <c r="D81" s="2" t="n">
-        <v>21844000</v>
-      </c>
+      <c r="C81" s="2" t="n">
+        <v>25007000</v>
+      </c>
+      <c r="D81" s="2" t="n"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Sarbon Yog'och AJ</t>
+          <t>Saodat Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>205262718</t>
+          <t>241704982</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>20208000045419893001</t>
+          <t>20208000405728734001</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -3461,136 +3461,136 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Shartnoma №180/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за транспортныеуслуги по договору №153/26</t>
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>5771000</v>
+        <v>25707000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="n">
-        <v>46255</v>
+        <v>46259</v>
       </c>
       <c r="B82" t="n">
         <v>174</v>
       </c>
-      <c r="C82" s="2" t="n"/>
-      <c r="D82" s="2" t="n">
-        <v>23381000</v>
-      </c>
+      <c r="C82" s="2" t="n">
+        <v>7301000</v>
+      </c>
+      <c r="D82" s="2" t="n"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Sarbon Yog'och AJ</t>
+          <t>Oltin Vodiy Non MChJ</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>205262718</t>
+          <t>337173119</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>20208000045419893001</t>
+          <t>20208000526338527001</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №3995 от 21.08.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за транспортные услуги по дог. №27/26</t>
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>29152000</v>
+        <v>18406000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="n">
-        <v>46255</v>
+        <v>46260</v>
       </c>
       <c r="B83" t="n">
         <v>175</v>
       </c>
-      <c r="C83" s="2" t="n">
-        <v>3120000</v>
-      </c>
-      <c r="D83" s="2" t="n"/>
+      <c r="C83" s="2" t="n"/>
+      <c r="D83" s="2" t="n">
+        <v>984000</v>
+      </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Gulshan Sut MChJ</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>395063017</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000719687187001</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Уплата налога на добавленную стоимость за июль</t>
+          <t>Оплата по счет-фактуре №5404 за поставленный товар</t>
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>26032000</v>
+        <v>19390000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="n">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="B84" t="n">
         <v>176</v>
       </c>
-      <c r="C84" s="2" t="n"/>
-      <c r="D84" s="2" t="n">
-        <v>19888000</v>
-      </c>
+      <c r="C84" s="2" t="n">
+        <v>9761000</v>
+      </c>
+      <c r="D84" s="2" t="n"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Sarbon Yog'och AJ</t>
+          <t>Durdona Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>205262718</t>
+          <t>264956936</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>20208000045419893001</t>
+          <t>20208000910514646001</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №1941 24.08.2026, QQS bilan</t>
+          <t>Оплата за упаковочные материалы, с/ф №8669</t>
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>45920000</v>
+        <v>9629000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="n">
-        <v>46258</v>
+        <v>46261</v>
       </c>
       <c r="B85" t="n">
         <v>177</v>
@@ -3611,141 +3611,141 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>20208000898561412001</t>
+          <t>20208000685415090001</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov</t>
+          <t>Elektr energiyasi uchun to'lov avgust</t>
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>44709000</v>
+        <v>8418000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="B86" t="n">
         <v>178</v>
       </c>
-      <c r="C86" s="2" t="n">
-        <v>34689000</v>
-      </c>
-      <c r="D86" s="2" t="n"/>
+      <c r="C86" s="2" t="n"/>
+      <c r="D86" s="2" t="n">
+        <v>3771000</v>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Farg'ona Polimer MChJ</t>
+          <t>Omad Yog'och MChJ</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>208253873</t>
+          <t>336272115</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>20208000580895696001</t>
+          <t>20208000872013636001</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №282/26 от 26.08.2026, НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №175/26, QQS 12%</t>
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>10020000</v>
+        <v>12189000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="n">
-        <v>46261</v>
+        <v>46265</v>
       </c>
       <c r="B87" t="n">
         <v>179</v>
       </c>
       <c r="C87" s="2" t="n"/>
       <c r="D87" s="2" t="n">
-        <v>5898000</v>
+        <v>10728000</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Sarbon Yog'och AJ</t>
+          <t>Marg'ilon Moy MChJ</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>205262718</t>
+          <t>302791508</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>20208000045419893001</t>
+          <t>20208000664381878001</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №4627 за поставленный товар</t>
+          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №7633</t>
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>15918000</v>
+        <v>22917000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B88" t="n">
         <v>180</v>
       </c>
-      <c r="C88" s="2" t="n">
-        <v>9183000</v>
-      </c>
-      <c r="D88" s="2" t="n"/>
+      <c r="C88" s="2" t="n"/>
+      <c r="D88" s="2" t="n">
+        <v>7796000</v>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Afrosiyob Plastik MChJ</t>
+          <t>Omad Yog'och MChJ</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>343417049</t>
+          <t>336272115</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>20208000274057287001</t>
+          <t>20208000872013636001</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТРАНСПОРТНЫЕ УСЛУГИ ПО ДОГОВОРУ №224/26</t>
+          <t>Оплата за продукцию по договору №245/26, НДС 12%</t>
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>6735000</v>
+        <v>30713000</v>
       </c>
     </row>
     <row r="89">
@@ -3755,23 +3755,18 @@
       <c r="B89" t="n">
         <v>181</v>
       </c>
-      <c r="C89" s="2" t="n"/>
-      <c r="D89" s="2" t="n">
-        <v>28688000</v>
-      </c>
+      <c r="C89" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D89" s="2" t="n"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Sarbon Yog'och AJ</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>205262718</t>
+          <t>Yangi Asr Bank</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>20208000045419893001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -3781,11 +3776,11 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №208/26, НДС 12%</t>
+          <t>Плата за SMS-информирование</t>
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>35423000</v>
+        <v>30413000</v>
       </c>
     </row>
     <row r="90">
@@ -3795,218 +3790,218 @@
       <c r="B90" t="n">
         <v>182</v>
       </c>
-      <c r="C90" s="2" t="n"/>
-      <c r="D90" s="2" t="n">
-        <v>6435000</v>
-      </c>
+      <c r="C90" s="2" t="n">
+        <v>12667000</v>
+      </c>
+      <c r="D90" s="2" t="n"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Namangan Plastik MChJ</t>
+          <t>Durdona Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>218371731</t>
+          <t>264956936</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>20208000915263385001</t>
+          <t>20208000910514646001</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №187/26, НДС 12%</t>
+          <t>Предоплата за материалы по договору №42/26</t>
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>41858000</v>
+        <v>17746000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="n">
-        <v>46265</v>
+        <v>46268</v>
       </c>
       <c r="B91" t="n">
         <v>183</v>
       </c>
-      <c r="C91" s="2" t="n"/>
-      <c r="D91" s="2" t="n">
-        <v>3620000</v>
-      </c>
+      <c r="C91" s="2" t="n">
+        <v>13626000</v>
+      </c>
+      <c r="D91" s="2" t="n"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Navoiy Non AJ</t>
+          <t>Oltin Vodiy Non MChJ</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>313296393</t>
+          <t>337173119</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>20208000809153157001</t>
+          <t>20208000526338527001</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №6842 за поставленный товар</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №267/26</t>
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>45478000</v>
+        <v>4120000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="n">
-        <v>46265</v>
+        <v>46269</v>
       </c>
       <c r="B92" t="n">
         <v>184</v>
       </c>
-      <c r="C92" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D92" s="2" t="n"/>
+      <c r="C92" s="2" t="n"/>
+      <c r="D92" s="2" t="n">
+        <v>67555000</v>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Yangi Asr Bank</t>
+          <t>Chust Poligraf MChJ</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>326271870</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000541989361001</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Комиссия за перевод</t>
+          <t>Оплата за продукцию по договору №23/26, НДС 12%</t>
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>45178000</v>
+        <v>71675000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="n">
-        <v>46265</v>
+        <v>46269</v>
       </c>
       <c r="B93" t="n">
         <v>185</v>
       </c>
-      <c r="C93" s="2" t="n">
-        <v>18309000</v>
-      </c>
-      <c r="D93" s="2" t="n"/>
+      <c r="C93" s="2" t="n"/>
+      <c r="D93" s="2" t="n">
+        <v>7711000</v>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Farg'ona Polimer MChJ</t>
+          <t>Omad Yog'och MChJ</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>208253873</t>
+          <t>336272115</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>20208000580895696001</t>
+          <t>20208000872013636001</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №42/26</t>
+          <t>Оплата по счет-фактуре №3784 за поставленный товар</t>
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>26869000</v>
+        <v>79386000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="n">
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="B94" t="n">
         <v>186</v>
       </c>
-      <c r="C94" s="2" t="n"/>
-      <c r="D94" s="2" t="n">
-        <v>8076000</v>
-      </c>
+      <c r="C94" s="2" t="n">
+        <v>4991000</v>
+      </c>
+      <c r="D94" s="2" t="n"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Sarbon Yog'och AJ</t>
+          <t>Andijon Yog'och MChJ</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>205262718</t>
+          <t>326745874</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>20208000045419893001</t>
+          <t>20208000918948325001</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №118/26, НДС 12%</t>
+          <t>Предоплата за материалы по дог. №87/26</t>
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>34945000</v>
+        <v>74395000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="n">
-        <v>46266</v>
+        <v>46270</v>
       </c>
       <c r="B95" t="n">
         <v>187</v>
       </c>
-      <c r="C95" s="2" t="n"/>
-      <c r="D95" s="2" t="n">
-        <v>1632000</v>
-      </c>
+      <c r="C95" s="2" t="n">
+        <v>8400000</v>
+      </c>
+      <c r="D95" s="2" t="n"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Sarbon Yog'och AJ</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>205262718</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-6371)</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>20208000045419893001</t>
+          <t>16307000301836844417</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4016,387 +4011,392 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Shartnoma №272/26 bo'yicha oldindan to'lov</t>
+          <t>Kredit shartnomasi L-2024-6371 bo'yicha navbatdagi to'lov (09.2026)</t>
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>36577000</v>
+        <v>65995000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="n">
-        <v>46267</v>
+        <v>46272</v>
       </c>
       <c r="B96" t="n">
         <v>188</v>
       </c>
       <c r="C96" s="2" t="n"/>
       <c r="D96" s="2" t="n">
-        <v>1987000</v>
+        <v>18214000</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Toshkent Savdo XK</t>
+          <t>Chust Poligraf MChJ</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>266276762</t>
+          <t>326271870</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>20208000028257633001</t>
+          <t>20208000541989361001</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №254/26 от 02.09.2026</t>
+          <t>Оплата за продукцию по договору №165/26, НДС 12%</t>
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>38564000</v>
+        <v>84209000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="n">
-        <v>46268</v>
+        <v>46272</v>
       </c>
       <c r="B97" t="n">
         <v>189</v>
       </c>
-      <c r="C97" s="2" t="n">
-        <v>3140000</v>
-      </c>
-      <c r="D97" s="2" t="n"/>
+      <c r="C97" s="2" t="n"/>
+      <c r="D97" s="2" t="n">
+        <v>6809000</v>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Navoiy Yog'och MChJ</t>
+          <t>Marg'ilon Moy MChJ</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>350649569</t>
+          <t>302791508</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>20208000649105146001</t>
+          <t>20208000664381878001</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по дог. №272/26</t>
+          <t>Предоплата за товар по договору №63/26 от 07.09.2026</t>
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>35424000</v>
+        <v>91018000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="n">
-        <v>46268</v>
+        <v>46272</v>
       </c>
       <c r="B98" t="n">
         <v>190</v>
       </c>
-      <c r="C98" s="2" t="n">
-        <v>17622000</v>
-      </c>
-      <c r="D98" s="2" t="n"/>
+      <c r="C98" s="2" t="n"/>
+      <c r="D98" s="2" t="n">
+        <v>5186000</v>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Farg'ona Polimer MChJ</t>
+          <t>Denov Yog'och MChJ</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>208253873</t>
+          <t>229639388</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>20208000580895696001</t>
+          <t>20208000915315775001</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА УПАКОВОЧНЫЕ МАТЕРИАЛЫ, С/Ф №2161</t>
+          <t>Оплата по счет-фактуре №4844 за поставленный товар</t>
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>17802000</v>
+        <v>96204000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="n">
-        <v>46268</v>
+        <v>46272</v>
       </c>
       <c r="B99" t="n">
         <v>191</v>
       </c>
       <c r="C99" s="2" t="n">
-        <v>61729000</v>
+        <v>1808000</v>
       </c>
       <c r="D99" s="2" t="n"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Farg'ona Polimer MChJ</t>
+          <t>Denov Qurilish MChJ</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>208253873</t>
+          <t>282538733</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>20208000580895696001</t>
+          <t>20208000808956968001</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №9652</t>
+          <t>Арендная плата за сентябрь 2026 г. по договору №24/25</t>
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>-43927000</v>
+        <v>94396000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="n">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="B100" t="n">
         <v>192</v>
       </c>
       <c r="C100" s="2" t="n">
-        <v>3725000</v>
+        <v>16078000</v>
       </c>
       <c r="D100" s="2" t="n"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Afrosiyob Plastik MChJ</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>343417049</t>
+          <t>Yangi Asr Bank</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>20208000274057287001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Оплата за сырье по дог. №295/26 от 04.09.2026, НДС 12%</t>
+          <t>Перечисление заработной платы за август 2026 г. согласно реестру №9287</t>
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>-47652000</v>
+        <v>78318000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B101" t="n">
         <v>193</v>
       </c>
       <c r="C101" s="2" t="n">
-        <v>4295000</v>
+        <v>17641000</v>
       </c>
       <c r="D101" s="2" t="n"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Afrosiyob Plastik MChJ</t>
+          <t>Oltin Vodiy Non MChJ</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>343417049</t>
+          <t>337173119</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>20208000274057287001</t>
+          <t>20208000526338527001</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №3061</t>
+          <t>Оплата за сырье по дог. №158/26 от 08.09.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>-51947000</v>
+        <v>60677000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="B102" t="n">
         <v>194</v>
       </c>
-      <c r="C102" s="2" t="n">
-        <v>16078000</v>
-      </c>
-      <c r="D102" s="2" t="n"/>
+      <c r="C102" s="2" t="n"/>
+      <c r="D102" s="2" t="n">
+        <v>10842000</v>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Yangi Asr Bank</t>
+          <t>Chust Poligraf MChJ</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>326271870</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000541989361001</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Перечисление заработной платы за август 2026 г. согласно реестру №7563</t>
+          <t>Предоплата за товар по договору №186/26 от 09.09.2026</t>
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>-68025000</v>
+        <v>71519000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="n">
-        <v>46270</v>
+        <v>46275</v>
       </c>
       <c r="B103" t="n">
         <v>195</v>
       </c>
-      <c r="C103" s="2" t="n">
-        <v>8400000</v>
-      </c>
-      <c r="D103" s="2" t="n"/>
+      <c r="C103" s="2" t="n"/>
+      <c r="D103" s="2" t="n">
+        <v>6599000</v>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-6371)</t>
+          <t>Marg'ilon Moy MChJ</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>302791508</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>16307000301836844417</t>
+          <t>20208000664381878001</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-6371 bo'yicha navbatdagi to'lov (09.2026)</t>
+          <t>Оплата по с/ф №8391 за поставленный товар</t>
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>-76425000</v>
+        <v>78118000</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="n">
-        <v>46272</v>
+        <v>46275</v>
       </c>
       <c r="B104" t="n">
         <v>196</v>
       </c>
       <c r="C104" s="2" t="n"/>
       <c r="D104" s="2" t="n">
-        <v>8079000</v>
+        <v>3914000</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Sarbon Yog'och AJ</t>
+          <t>Chust Poligraf MChJ</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>205262718</t>
+          <t>326271870</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>20208000045419893001</t>
+          <t>20208000541989361001</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №232/26 от 07.09.2026</t>
+          <t>Оплата по счет-фактуре №6336 за поставленный товар</t>
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>-68346000</v>
+        <v>82032000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="n">
-        <v>46272</v>
+        <v>46276</v>
       </c>
       <c r="B105" t="n">
         <v>197</v>
       </c>
       <c r="C105" s="2" t="n"/>
       <c r="D105" s="2" t="n">
-        <v>2226000</v>
+        <v>16317000</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Sarbon Yog'och AJ</t>
+          <t>Omad Yog'och MChJ</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>205262718</t>
+          <t>336272115</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>20208000045419893001</t>
+          <t>20208000872013636001</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -4406,437 +4406,437 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №9857 от 07.09.2026, в т.ч. НДС 12%</t>
+          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №3577 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>-66120000</v>
+        <v>98349000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="n">
-        <v>46272</v>
+        <v>46279</v>
       </c>
       <c r="B106" t="n">
         <v>198</v>
       </c>
       <c r="C106" s="2" t="n"/>
       <c r="D106" s="2" t="n">
-        <v>1617000</v>
+        <v>6083000</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Toshkent Savdo XK</t>
+          <t>Chust Poligraf MChJ</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>266276762</t>
+          <t>326271870</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>20208000028257633001</t>
+          <t>20208000541989361001</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №6092 за поставленный товар</t>
+          <t>Оплата за товар по счет-фактуре №4649 от 14.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>-64503000</v>
+        <v>104432000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="n">
-        <v>46272</v>
+        <v>46279</v>
       </c>
       <c r="B107" t="n">
         <v>199</v>
       </c>
       <c r="C107" s="2" t="n"/>
       <c r="D107" s="2" t="n">
-        <v>1318000</v>
+        <v>3787000</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Sarbon Yog'och AJ</t>
+          <t>Chust Poligraf MChJ</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>205262718</t>
+          <t>326271870</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>20208000045419893001</t>
+          <t>20208000541989361001</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №6307 за поставленный товар</t>
+          <t>Mahsulot uchun to'lov, shartn. №156/26, QQS 12%</t>
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>-63185000</v>
+        <v>108219000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="n">
-        <v>46272</v>
+        <v>46279</v>
       </c>
       <c r="B108" t="n">
         <v>200</v>
       </c>
       <c r="C108" s="2" t="n">
-        <v>1808000</v>
+        <v>7486000</v>
       </c>
       <c r="D108" s="2" t="n"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Marg'ilon Qurilish MChJ</t>
+          <t>Oltin Vodiy Non MChJ</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>354150901</t>
+          <t>337173119</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>20208000960261721001</t>
+          <t>20208000526338527001</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Аренда помещения за сентябрь, дог. №77/23</t>
+          <t>Оплата за товары соглсно с/ф №7924</t>
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>-64993000</v>
+        <v>100733000</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="n">
-        <v>46272</v>
+        <v>46280</v>
       </c>
       <c r="B109" t="n">
         <v>201</v>
       </c>
-      <c r="C109" s="2" t="n">
-        <v>2386000</v>
-      </c>
-      <c r="D109" s="2" t="n"/>
+      <c r="C109" s="2" t="n"/>
+      <c r="D109" s="2" t="n">
+        <v>6874000</v>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Afrosiyob Plastik MChJ</t>
+          <t>Marg'ilon Moy MChJ</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>343417049</t>
+          <t>302791508</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>20208000274057287001</t>
+          <t>20208000664381878001</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №5360</t>
+          <t>Оплата за товар по счет-фактуре №6670 от 15.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>-67379000</v>
+        <v>107607000</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="n">
-        <v>46272</v>
+        <v>46280</v>
       </c>
       <c r="B110" t="n">
         <v>202</v>
       </c>
       <c r="C110" s="2" t="n">
-        <v>15971000</v>
+        <v>37199000</v>
       </c>
       <c r="D110" s="2" t="n"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Afrosiyob Plastik MChJ</t>
+          <t>Oltin Vodiy Non MChJ</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>343417049</t>
+          <t>337173119</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>20208000274057287001</t>
+          <t>20208000526338527001</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №4498</t>
+          <t>Оплата за транспортные услуги по договору №122/26</t>
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>-83350000</v>
+        <v>70408000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="n">
-        <v>46273</v>
+        <v>46281</v>
       </c>
       <c r="B111" t="n">
         <v>203</v>
       </c>
-      <c r="C111" s="2" t="n">
-        <v>34187000</v>
-      </c>
-      <c r="D111" s="2" t="n"/>
+      <c r="C111" s="2" t="n"/>
+      <c r="D111" s="2" t="n">
+        <v>7848000</v>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Tong Qurilish MChJ</t>
+          <t>Chust Poligraf MChJ</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>325307809</t>
+          <t>326271870</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>20208000468403398001</t>
+          <t>20208000541989361001</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №4428</t>
+          <t>Оплата за продукцию по дог. №202/26, НДС 12%</t>
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>-117537000</v>
+        <v>78256000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="n">
-        <v>46274</v>
+        <v>46281</v>
       </c>
       <c r="B112" t="n">
         <v>204</v>
       </c>
-      <c r="C112" s="2" t="n"/>
-      <c r="D112" s="2" t="n">
-        <v>3262000</v>
-      </c>
+      <c r="C112" s="2" t="n">
+        <v>2193000</v>
+      </c>
+      <c r="D112" s="2" t="n"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Navoiy Non AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>313296393</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>20208000809153157001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №339 от 09.09.2026, в т.ч. НДС 12%</t>
+          <t>Avgust oyi uchun ijtimoiy soliq</t>
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>-114275000</v>
+        <v>76063000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="n">
-        <v>46274</v>
+        <v>46281</v>
       </c>
       <c r="B113" t="n">
         <v>205</v>
       </c>
       <c r="C113" s="2" t="n">
-        <v>18865000</v>
+        <v>2193000</v>
       </c>
       <c r="D113" s="2" t="n"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Tong Qurilish MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>325307809</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>20208000468403398001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №9359</t>
+          <t>Налог на доходы физических лиц за август 2026 г.</t>
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>-133140000</v>
+        <v>73870000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="n">
-        <v>46276</v>
+        <v>46282</v>
       </c>
       <c r="B114" t="n">
         <v>206</v>
       </c>
       <c r="C114" s="2" t="n"/>
       <c r="D114" s="2" t="n">
-        <v>8023000</v>
+        <v>3804000</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Sarbon Yog'och AJ</t>
+          <t>Marg'ilon Moy MChJ</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>205262718</t>
+          <t>302791508</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>20208000045419893001</t>
+          <t>20208000664381878001</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №2306 от 11.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата по счет-фактуре №5574 за поставленный товар</t>
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>-125117000</v>
+        <v>77674000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="n">
-        <v>46276</v>
+        <v>46283</v>
       </c>
       <c r="B115" t="n">
         <v>207</v>
       </c>
-      <c r="C115" s="2" t="n">
-        <v>4005000</v>
-      </c>
-      <c r="D115" s="2" t="n"/>
+      <c r="C115" s="2" t="n"/>
+      <c r="D115" s="2" t="n">
+        <v>6715000</v>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Farg'ona Polimer MChJ</t>
+          <t>Denov Yog'och MChJ</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>208253873</t>
+          <t>229639388</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>20208000580895696001</t>
+          <t>20208000915315775001</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №6529</t>
+          <t>Mahsulot uchun to'lov, shartnoma №120/26, QQS 12%</t>
         </is>
       </c>
       <c r="J115" s="2" t="n">
-        <v>-129122000</v>
+        <v>84389000</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="n">
-        <v>46279</v>
+        <v>46286</v>
       </c>
       <c r="B116" t="n">
         <v>208</v>
       </c>
       <c r="C116" s="2" t="n"/>
       <c r="D116" s="2" t="n">
-        <v>1809000</v>
+        <v>5904000</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Sarbon Yog'och AJ</t>
+          <t>Omad Yog'och MChJ</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>205262718</t>
+          <t>336272115</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>20208000045419893001</t>
+          <t>20208000872013636001</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -4846,157 +4846,157 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №2561 14.09.2026, QQS bilan</t>
+          <t>Mahsulot uchun to'lov, shartnoma №245/26, QQS 12%</t>
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>-127313000</v>
+        <v>90293000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="n">
-        <v>46279</v>
+        <v>46286</v>
       </c>
       <c r="B117" t="n">
         <v>209</v>
       </c>
       <c r="C117" s="2" t="n"/>
       <c r="D117" s="2" t="n">
-        <v>1339000</v>
+        <v>4945000</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Bunyodkor Avto Savdo AJ</t>
+          <t>Farg'ona Yog'och MChJ</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>368027915</t>
+          <t>313166428</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>20208000856643818001</t>
+          <t>20208000417565217001</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №5841 за поставленный товар</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №4572</t>
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>-125974000</v>
+        <v>95238000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="n">
-        <v>46279</v>
+        <v>46286</v>
       </c>
       <c r="B118" t="n">
         <v>210</v>
       </c>
-      <c r="C118" s="2" t="n">
-        <v>1994000</v>
-      </c>
-      <c r="D118" s="2" t="n"/>
+      <c r="C118" s="2" t="n"/>
+      <c r="D118" s="2" t="n">
+        <v>3604000</v>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Afrosiyob Plastik MChJ</t>
+          <t>Chust Poligraf MChJ</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>343417049</t>
+          <t>326271870</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>20208000274057287001</t>
+          <t>20208000541989361001</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №231/26</t>
+          <t>Предоплата за товар по дог. №91/26 от 21.09.2026</t>
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>-127968000</v>
+        <v>98842000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="n">
-        <v>46279</v>
+        <v>46286</v>
       </c>
       <c r="B119" t="n">
         <v>211</v>
       </c>
-      <c r="C119" s="2" t="n">
-        <v>3984000</v>
-      </c>
-      <c r="D119" s="2" t="n"/>
+      <c r="C119" s="2" t="n"/>
+      <c r="D119" s="2" t="n">
+        <v>3300000</v>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Tong Qurilish MChJ</t>
+          <t>Chust Poligraf MChJ</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>325307809</t>
+          <t>326271870</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>20208000468403398001</t>
+          <t>20208000541989361001</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №6569</t>
+          <t>Shartnoma №43/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>-131952000</v>
+        <v>102142000</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="n">
-        <v>46279</v>
+        <v>46286</v>
       </c>
       <c r="B120" t="n">
         <v>212</v>
       </c>
       <c r="C120" s="2" t="n">
-        <v>9593000</v>
+        <v>7051000</v>
       </c>
       <c r="D120" s="2" t="n"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Farg'ona Polimer MChJ</t>
+          <t>Durdona Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>208253873</t>
+          <t>264956936</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>20208000580895696001</t>
+          <t>20208000910514646001</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -5006,397 +5006,397 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №68/26</t>
+          <t>Предоплата за материалы по договору №165/26</t>
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>-141545000</v>
+        <v>95091000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="3" t="n">
-        <v>46279</v>
+        <v>46287</v>
       </c>
       <c r="B121" t="n">
         <v>213</v>
       </c>
-      <c r="C121" s="2" t="n">
-        <v>10762000</v>
-      </c>
-      <c r="D121" s="2" t="n"/>
+      <c r="C121" s="2" t="n"/>
+      <c r="D121" s="2" t="n">
+        <v>4901000</v>
+      </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Afrosiyob Plastik MChJ</t>
+          <t>Marg'ilon Moy MChJ</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>343417049</t>
+          <t>302791508</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>20208000274057287001</t>
+          <t>20208000664381878001</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №214/26</t>
+          <t>Оплата по счет-фактуре №1914 за поставленный товар</t>
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>-152307000</v>
+        <v>99992000</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="3" t="n">
-        <v>46280</v>
+        <v>46287</v>
       </c>
       <c r="B122" t="n">
         <v>214</v>
       </c>
       <c r="C122" s="2" t="n"/>
       <c r="D122" s="2" t="n">
-        <v>13305000</v>
+        <v>4084000</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Bunyodkor Avto Savdo AJ</t>
+          <t>Farg'ona Yog'och MChJ</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>368027915</t>
+          <t>313166428</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>20208000856643818001</t>
+          <t>20208000417565217001</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №56/26 от 15.09.2026</t>
+          <t>Предоплата за товар по договору №256/26 от 22.09.2026</t>
         </is>
       </c>
       <c r="J122" s="2" t="n">
-        <v>-139002000</v>
+        <v>104076000</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="3" t="n">
-        <v>46280</v>
+        <v>46287</v>
       </c>
       <c r="B123" t="n">
         <v>215</v>
       </c>
-      <c r="C123" s="2" t="n"/>
-      <c r="D123" s="2" t="n">
-        <v>12465000</v>
-      </c>
+      <c r="C123" s="2" t="n">
+        <v>3131000</v>
+      </c>
+      <c r="D123" s="2" t="n"/>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Sarbon Yog'och AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>205262718</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>20208000045419893001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №2194 за поставленный товар</t>
+          <t>Уплата налога на добавленную стоимость за август</t>
         </is>
       </c>
       <c r="J123" s="2" t="n">
-        <v>-126537000</v>
+        <v>100945000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="3" t="n">
-        <v>46280</v>
+        <v>46287</v>
       </c>
       <c r="B124" t="n">
         <v>216</v>
       </c>
       <c r="C124" s="2" t="n">
-        <v>2193000</v>
+        <v>8380000</v>
       </c>
       <c r="D124" s="2" t="n"/>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Oltin Vodiy Non MChJ</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>337173119</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000526338527001</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Социальный налог за август 2026 г.</t>
+          <t>Оплата за товары согласно счет-фактуре №628</t>
         </is>
       </c>
       <c r="J124" s="2" t="n">
-        <v>-128730000</v>
+        <v>92565000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="n">
-        <v>46280</v>
+        <v>46287</v>
       </c>
       <c r="B125" t="n">
         <v>217</v>
       </c>
       <c r="C125" s="2" t="n">
-        <v>2193000</v>
+        <v>10978000</v>
       </c>
       <c r="D125" s="2" t="n"/>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Oltin Vodiy Non MChJ</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>337173119</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000526338527001</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>НДФЛ за август 2026</t>
+          <t>ПРЕДОПЛАТА ЗА МАТЕРИАЛЫ ПО ДОГ. №126/26</t>
         </is>
       </c>
       <c r="J125" s="2" t="n">
-        <v>-130923000</v>
+        <v>81587000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="3" t="n">
-        <v>46282</v>
+        <v>46287</v>
       </c>
       <c r="B126" t="n">
         <v>218</v>
       </c>
-      <c r="C126" s="2" t="n"/>
-      <c r="D126" s="2" t="n">
-        <v>53903000</v>
-      </c>
+      <c r="C126" s="2" t="n">
+        <v>19009000</v>
+      </c>
+      <c r="D126" s="2" t="n"/>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Sarbon Yog'och AJ</t>
+          <t>Oltin Vodiy Non MChJ</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>205262718</t>
+          <t>337173119</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>20208000045419893001</t>
+          <t>20208000526338527001</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №7429 за поставленный товар</t>
+          <t>Materiallar uchun oldindan to'lov, shartn. №37/26</t>
         </is>
       </c>
       <c r="J126" s="2" t="n">
-        <v>-77020000</v>
+        <v>62578000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="3" t="n">
-        <v>46282</v>
+        <v>46289</v>
       </c>
       <c r="B127" t="n">
         <v>219</v>
       </c>
       <c r="C127" s="2" t="n"/>
       <c r="D127" s="2" t="n">
-        <v>9431000</v>
+        <v>31987000</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Sarbon Yog'och AJ</t>
+          <t>Chust Poligraf MChJ</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>205262718</t>
+          <t>326271870</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>20208000045419893001</t>
+          <t>20208000541989361001</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №199/26 от 17.09.2026</t>
+          <t>Оплата за товар по счет-фактуре №587 от 24.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J127" s="2" t="n">
-        <v>-67589000</v>
+        <v>94565000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="3" t="n">
-        <v>46282</v>
+        <v>46289</v>
       </c>
       <c r="B128" t="n">
         <v>220</v>
       </c>
       <c r="C128" s="2" t="n"/>
       <c r="D128" s="2" t="n">
-        <v>4766000</v>
+        <v>5466000</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Bunyodkor Avto Savdo AJ</t>
+          <t>Chust Poligraf MChJ</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>368027915</t>
+          <t>326271870</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>20208000856643818001</t>
+          <t>20208000541989361001</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №3131 за поставленный товар</t>
+          <t>Предоплата за товар по договору №134/26 от 24.09.2026</t>
         </is>
       </c>
       <c r="J128" s="2" t="n">
-        <v>-62823000</v>
+        <v>100031000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="3" t="n">
-        <v>46283</v>
+        <v>46290</v>
       </c>
       <c r="B129" t="n">
         <v>221</v>
       </c>
       <c r="C129" s="2" t="n"/>
       <c r="D129" s="2" t="n">
-        <v>6624000</v>
+        <v>10321000</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Bunyodkor Avto Savdo AJ</t>
+          <t>Chust Poligraf MChJ</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>368027915</t>
+          <t>326271870</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>20208000856643818001</t>
+          <t>20208000541989361001</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Shartnoma №77/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата по счет-фактуре №7251 за поставленный товар</t>
         </is>
       </c>
       <c r="J129" s="2" t="n">
-        <v>-56199000</v>
+        <v>110352000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="3" t="n">
-        <v>46283</v>
+        <v>46290</v>
       </c>
       <c r="B130" t="n">
         <v>222</v>
       </c>
-      <c r="C130" s="2" t="n"/>
-      <c r="D130" s="2" t="n">
-        <v>3139000</v>
-      </c>
+      <c r="C130" s="2" t="n">
+        <v>7151000</v>
+      </c>
+      <c r="D130" s="2" t="n"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Bunyodkor Avto Savdo AJ</t>
+          <t>Oltin Vodiy Non MChJ</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>368027915</t>
+          <t>337173119</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>20208000856643818001</t>
+          <t>20208000526338527001</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -5406,117 +5406,117 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №83/26, QQS 12%</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №66/26</t>
         </is>
       </c>
       <c r="J130" s="2" t="n">
-        <v>-53060000</v>
+        <v>103201000</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="3" t="n">
-        <v>46283</v>
+        <v>46290</v>
       </c>
       <c r="B131" t="n">
         <v>223</v>
       </c>
-      <c r="C131" s="2" t="n"/>
-      <c r="D131" s="2" t="n">
-        <v>1360000</v>
-      </c>
+      <c r="C131" s="2" t="n">
+        <v>11084000</v>
+      </c>
+      <c r="D131" s="2" t="n"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Sarbon Yog'och AJ</t>
+          <t>Andijon Yog'och MChJ</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>205262718</t>
+          <t>326745874</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>20208000045419893001</t>
+          <t>20208000918948325001</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №2816 от 18.09.2026, в т.ч. НДС 12%</t>
+          <t>Materiallar uchun oldindan to'lov, shartn. №168/26</t>
         </is>
       </c>
       <c r="J131" s="2" t="n">
-        <v>-51700000</v>
+        <v>92117000</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="3" t="n">
-        <v>46286</v>
+        <v>46293</v>
       </c>
       <c r="B132" t="n">
         <v>224</v>
       </c>
-      <c r="C132" s="2" t="n"/>
-      <c r="D132" s="2" t="n">
-        <v>1909000</v>
-      </c>
+      <c r="C132" s="2" t="n">
+        <v>1130000</v>
+      </c>
+      <c r="D132" s="2" t="n"/>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Navoiy Non AJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>313296393</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>20208000809153157001</t>
+          <t>20208000685415090001</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>SHARTNOMA №151/26 BO'YICHA OLDINDAN TO'LOV</t>
+          <t>Elektr energiyasi uchun to'lov sentyabr</t>
         </is>
       </c>
       <c r="J132" s="2" t="n">
-        <v>-49791000</v>
+        <v>90987000</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="3" t="n">
-        <v>46286</v>
+        <v>46294</v>
       </c>
       <c r="B133" t="n">
         <v>225</v>
       </c>
-      <c r="C133" s="2" t="n">
-        <v>1818000</v>
-      </c>
-      <c r="D133" s="2" t="n"/>
+      <c r="C133" s="2" t="n"/>
+      <c r="D133" s="2" t="n">
+        <v>8180000</v>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Farg'ona Polimer MChJ</t>
+          <t>Chust Poligraf MChJ</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>208253873</t>
+          <t>326271870</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>20208000580895696001</t>
+          <t>20208000541989361001</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -5526,117 +5526,112 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №88/26</t>
+          <t>Оплата за товар по счет-фактуре №8734 от 29.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J133" s="2" t="n">
-        <v>-51609000</v>
+        <v>99167000</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="3" t="n">
-        <v>46286</v>
+        <v>46295</v>
       </c>
       <c r="B134" t="n">
         <v>226</v>
       </c>
       <c r="C134" s="2" t="n">
-        <v>2998000</v>
+        <v>300000</v>
       </c>
       <c r="D134" s="2" t="n"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>201122905</t>
+          <t>Yangi Asr Bank</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>НДС за август 2026 г.</t>
+          <t>Hisob-kassa xizmati uchun haq</t>
         </is>
       </c>
       <c r="J134" s="2" t="n">
-        <v>-54607000</v>
+        <v>98867000</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="3" t="n">
-        <v>46287</v>
+        <v>46295</v>
       </c>
       <c r="B135" t="n">
         <v>227</v>
       </c>
-      <c r="C135" s="2" t="n"/>
-      <c r="D135" s="2" t="n">
-        <v>63775000</v>
-      </c>
+      <c r="C135" s="2" t="n">
+        <v>7690000</v>
+      </c>
+      <c r="D135" s="2" t="n"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Sarbon Yog'och AJ</t>
+          <t>Oltin Vodiy Non MChJ</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>205262718</t>
+          <t>337173119</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>20208000045419893001</t>
+          <t>20208000526338527001</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №9563 от 22.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товары согласно счет-фактуре №5311</t>
         </is>
       </c>
       <c r="J135" s="2" t="n">
-        <v>9168000</v>
+        <v>91177000</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="3" t="n">
-        <v>46288</v>
+        <v>46295</v>
       </c>
       <c r="B136" t="n">
         <v>228</v>
       </c>
-      <c r="C136" s="2" t="n"/>
-      <c r="D136" s="2" t="n">
-        <v>15496000</v>
-      </c>
+      <c r="C136" s="2" t="n">
+        <v>61877000</v>
+      </c>
+      <c r="D136" s="2" t="n"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Bunyodkor Avto Savdo AJ</t>
+          <t>Oltin Vodiy Non MChJ</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>368027915</t>
+          <t>337173119</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>20208000856643818001</t>
+          <t>20208000526338527001</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -5646,551 +5641,36 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №29/26, НДС 12%</t>
+          <t>Оплата за сырье по договору №63/26 от 30.09.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J136" s="2" t="n">
-        <v>24664000</v>
+        <v>29300000</v>
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="3" t="n">
-        <v>46289</v>
-      </c>
-      <c r="B137" t="n">
-        <v>229</v>
-      </c>
-      <c r="C137" s="2" t="n">
-        <v>1130000</v>
-      </c>
-      <c r="D137" s="2" t="n"/>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>200933985</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>20208000898561412001</t>
-        </is>
-      </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>Оплата за электроэнергию согласно счету</t>
-        </is>
-      </c>
-      <c r="J137" s="2" t="n">
-        <v>23534000</v>
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Итого обороты:</t>
+        </is>
+      </c>
+      <c r="C137" s="4" t="n">
+        <v>798790000</v>
+      </c>
+      <c r="D137" s="4" t="n">
+        <v>794990000</v>
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="3" t="n">
-        <v>46290</v>
-      </c>
-      <c r="B138" t="n">
-        <v>230</v>
-      </c>
-      <c r="C138" s="2" t="n"/>
-      <c r="D138" s="2" t="n">
-        <v>3026000</v>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>Sarbon Yog'och AJ</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>205262718</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>20208000045419893001</t>
-        </is>
-      </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>Shartnoma №218/26 bo'yicha oldindan to'lov</t>
-        </is>
-      </c>
-      <c r="J138" s="2" t="n">
-        <v>26560000</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="3" t="n">
-        <v>46290</v>
-      </c>
-      <c r="B139" t="n">
-        <v>231</v>
-      </c>
-      <c r="C139" s="2" t="n"/>
-      <c r="D139" s="2" t="n">
-        <v>1643000</v>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>Bunyodkor Avto Savdo AJ</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>368027915</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>20208000856643818001</t>
-        </is>
-      </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>Предоплата за товар по дог. №237/26 от 25.09.2026</t>
-        </is>
-      </c>
-      <c r="J139" s="2" t="n">
-        <v>28203000</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="3" t="n">
-        <v>46290</v>
-      </c>
-      <c r="B140" t="n">
-        <v>232</v>
-      </c>
-      <c r="C140" s="2" t="n">
-        <v>2782000</v>
-      </c>
-      <c r="D140" s="2" t="n"/>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>Farg'ona Polimer MChJ</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>208253873</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>20208000580895696001</t>
-        </is>
-      </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>Оплата за транспортные услуги по договору №84/26</t>
-        </is>
-      </c>
-      <c r="J140" s="2" t="n">
-        <v>25421000</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B141" t="n">
-        <v>233</v>
-      </c>
-      <c r="C141" s="2" t="n"/>
-      <c r="D141" s="2" t="n">
-        <v>2758000</v>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>Sarbon Yog'och AJ</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>205262718</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>20208000045419893001</t>
-        </is>
-      </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №6742 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
-        </is>
-      </c>
-      <c r="J141" s="2" t="n">
-        <v>28179000</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B142" t="n">
-        <v>234</v>
-      </c>
-      <c r="C142" s="2" t="n"/>
-      <c r="D142" s="2" t="n">
-        <v>2011000</v>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>Bunyodkor Avto Savdo AJ</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>368027915</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>20208000856643818001</t>
-        </is>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>Оплата по счет-фактуре №2655 за поставленный товар</t>
-        </is>
-      </c>
-      <c r="J142" s="2" t="n">
-        <v>30190000</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B143" t="n">
-        <v>235</v>
-      </c>
-      <c r="C143" s="2" t="n">
-        <v>2499000</v>
-      </c>
-      <c r="D143" s="2" t="n"/>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>Farg'ona Polimer MChJ</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>208253873</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>20208000580895696001</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>Оплата за сырье по договору №214/26 от 28.09.2026, НДС 12%</t>
-        </is>
-      </c>
-      <c r="J143" s="2" t="n">
-        <v>27691000</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="3" t="n">
-        <v>46294</v>
-      </c>
-      <c r="B144" t="n">
-        <v>236</v>
-      </c>
-      <c r="C144" s="2" t="n"/>
-      <c r="D144" s="2" t="n">
-        <v>1946000</v>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>Toshkent Savdo XK</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>266276762</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>20208000028257633001</t>
-        </is>
-      </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>Оплата за продукцию по договору №199/26, НДС 12%</t>
-        </is>
-      </c>
-      <c r="J144" s="2" t="n">
-        <v>29637000</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="3" t="n">
-        <v>46294</v>
-      </c>
-      <c r="B145" t="n">
-        <v>237</v>
-      </c>
-      <c r="C145" s="2" t="n">
-        <v>5540000</v>
-      </c>
-      <c r="D145" s="2" t="n"/>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>Afrosiyob Plastik MChJ</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>343417049</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>20208000274057287001</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №45/26</t>
-        </is>
-      </c>
-      <c r="J145" s="2" t="n">
-        <v>24097000</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="3" t="n">
-        <v>46294</v>
-      </c>
-      <c r="B146" t="n">
-        <v>238</v>
-      </c>
-      <c r="C146" s="2" t="n">
-        <v>7384000</v>
-      </c>
-      <c r="D146" s="2" t="n"/>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>Tong Qurilish MChJ</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>325307809</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>20208000468403398001</t>
-        </is>
-      </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>Оплата за упаковочные материалы, с/ф №4064</t>
-        </is>
-      </c>
-      <c r="J146" s="2" t="n">
-        <v>16713000</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="3" t="n">
-        <v>46295</v>
-      </c>
-      <c r="B147" t="n">
-        <v>239</v>
-      </c>
-      <c r="C147" s="2" t="n"/>
-      <c r="D147" s="2" t="n">
-        <v>10430000</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>Sarbon Yog'och AJ</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>205262718</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>20208000045419893001</t>
-        </is>
-      </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>Предоплата за товар по дог. №289/26 от 30.09.2026</t>
-        </is>
-      </c>
-      <c r="J147" s="2" t="n">
-        <v>27143000</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="3" t="n">
-        <v>46295</v>
-      </c>
-      <c r="B148" t="n">
-        <v>240</v>
-      </c>
-      <c r="C148" s="2" t="n"/>
-      <c r="D148" s="2" t="n">
-        <v>2457000</v>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>Sarbon Yog'och AJ</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>205262718</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>20208000045419893001</t>
-        </is>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №1642</t>
-        </is>
-      </c>
-      <c r="J148" s="2" t="n">
-        <v>29600000</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="3" t="n">
-        <v>46295</v>
-      </c>
-      <c r="B149" t="n">
-        <v>241</v>
-      </c>
-      <c r="C149" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D149" s="2" t="n"/>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>Yangi Asr Bank</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>45994000900000001001</t>
-        </is>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>Комиссия за перевод</t>
-        </is>
-      </c>
-      <c r="J149" s="2" t="n">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Исходящий остаток на 30.09.2026:</t>
+        </is>
+      </c>
+      <c r="C138" s="4" t="n">
         <v>29300000</v>
       </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Итого обороты:</t>
-        </is>
-      </c>
-      <c r="C150" s="4" t="n">
-        <v>792668000</v>
-      </c>
-      <c r="D150" s="4" t="n">
-        <v>788868000</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Исходящий остаток на 30.09.2026:</t>
-        </is>
-      </c>
-      <c r="C151" s="4" t="n">
-        <v>29300000</v>
-      </c>
-      <c r="D151" s="4" t="n"/>
+      <c r="D138" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
